--- a/docs/keyboard-shortcuts.xlsx
+++ b/docs/keyboard-shortcuts.xlsx
@@ -681,7 +681,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Clipboard</t>
         </is>
       </c>
       <c r="B15" s="4">
@@ -704,7 +704,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Clipboard</t>
+          <t>Dictation</t>
         </is>
       </c>
       <c r="B16" s="4">
@@ -727,7 +727,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Dictation</t>
+          <t>Yours</t>
         </is>
       </c>
       <c r="B17" s="4">
@@ -750,7 +750,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Yours</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="B18" s="4">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Super + W</t>
+          <t>Super + Left</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>Close window</t>
+          <t>Focus on left window</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="G2" s="10" t="n"/>
@@ -2178,12 +2178,12 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Ctrl + Alt + Delete</t>
+          <t>Super + Right</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Close all windows</t>
+          <t>Focus on right window</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
@@ -2198,14 +2198,10 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
       <c r="H3" s="9" t="inlineStr"/>
     </row>
     <row r="4">
@@ -2214,12 +2210,12 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Super + J</t>
+          <t>Super + Up</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Toggle window split</t>
+          <t>Focus on above window</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -2234,14 +2230,10 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n"/>
       <c r="H4" s="9" t="inlineStr"/>
     </row>
     <row r="5">
@@ -2250,12 +2242,12 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Super + P</t>
+          <t>Super + Down</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Pseudo window</t>
+          <t>Focus on below window</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2270,14 +2262,10 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n"/>
       <c r="H5" s="9" t="inlineStr"/>
     </row>
     <row r="6">
@@ -2286,12 +2274,12 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Super + T</t>
+          <t>Super + 1</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Toggle window floating/tiling</t>
+          <t>Switch to workspace 1</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -2306,7 +2294,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="G6" s="10" t="n"/>
@@ -2318,12 +2306,12 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Super + F</t>
+          <t>Super + Shift + 1</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Full screen</t>
+          <t>Move window to workspace 1</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -2338,7 +2326,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="G7" s="10" t="n"/>
@@ -2350,12 +2338,12 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + F</t>
+          <t>Super + Shift + Alt + 1</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Tiled full screen</t>
+          <t>Move window silently to workspace 1</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -2370,14 +2358,10 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n"/>
       <c r="H8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
@@ -2386,12 +2370,12 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + F</t>
+          <t>Super + 2</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Full width</t>
+          <t>Switch to workspace 2</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -2406,14 +2390,10 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n"/>
       <c r="H9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -2422,12 +2402,12 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Super + O</t>
+          <t>Super + Shift + 2</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Pop window out (float &amp; pin)</t>
+          <t>Move window to workspace 2</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -2442,14 +2422,10 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>Remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="n"/>
       <c r="H10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
@@ -2458,12 +2434,12 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + Home</t>
+          <t>Super + Shift + Alt + 2</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Save window width</t>
+          <t>Move window silently to workspace 2</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -2478,14 +2454,10 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>Remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="n"/>
       <c r="H11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
@@ -2494,12 +2466,12 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Super + Home</t>
+          <t>Super + 3</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Restore window width</t>
+          <t>Switch to workspace 3</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -2514,14 +2486,10 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="n"/>
       <c r="H12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
@@ -2530,12 +2498,12 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Super + L</t>
+          <t>Super + Shift + 3</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Toggle workspace layout</t>
+          <t>Move window to workspace 3</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -2550,14 +2518,10 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="n"/>
       <c r="H13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
@@ -2566,12 +2530,12 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Super + Left</t>
+          <t>Super + Shift + Alt + 3</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Focus on left window</t>
+          <t>Move window silently to workspace 3</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -2598,12 +2562,12 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Super + Right</t>
+          <t>Super + 4</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Focus on right window</t>
+          <t>Switch to workspace 4</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -2630,12 +2594,12 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Super + Up</t>
+          <t>Super + Shift + 4</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Focus on above window</t>
+          <t>Move window to workspace 4</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -2662,12 +2626,12 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Super + Down</t>
+          <t>Super + Shift + Alt + 4</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Focus on below window</t>
+          <t>Move window silently to workspace 4</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -2694,12 +2658,12 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Super + 1</t>
+          <t>Super + 5</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Switch to workspace 1</t>
+          <t>Switch to workspace 5</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -2726,12 +2690,12 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + 1</t>
+          <t>Super + Shift + 5</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Move window to workspace 1</t>
+          <t>Move window to workspace 5</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -2758,12 +2722,12 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + 1</t>
+          <t>Super + Shift + Alt + 5</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Move window silently to workspace 1</t>
+          <t>Move window silently to workspace 5</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -2790,12 +2754,12 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Super + 2</t>
+          <t>Super + 6</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Switch to workspace 2</t>
+          <t>Switch to workspace 6</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -2822,12 +2786,12 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + 2</t>
+          <t>Super + Shift + 6</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Move window to workspace 2</t>
+          <t>Move window to workspace 6</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -2854,12 +2818,12 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + 2</t>
+          <t>Super + Shift + Alt + 6</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Move window silently to workspace 2</t>
+          <t>Move window silently to workspace 6</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -2886,12 +2850,12 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Super + 3</t>
+          <t>Super + 7</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Switch to workspace 3</t>
+          <t>Switch to workspace 7</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -2918,12 +2882,12 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + 3</t>
+          <t>Super + Shift + 7</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Move window to workspace 3</t>
+          <t>Move window to workspace 7</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -2950,12 +2914,12 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + 3</t>
+          <t>Super + Shift + Alt + 7</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Move window silently to workspace 3</t>
+          <t>Move window silently to workspace 7</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -2982,12 +2946,12 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Super + 4</t>
+          <t>Super + 8</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Switch to workspace 4</t>
+          <t>Switch to workspace 8</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -3014,12 +2978,12 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + 4</t>
+          <t>Super + Shift + 8</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Move window to workspace 4</t>
+          <t>Move window to workspace 8</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -3046,12 +3010,12 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + 4</t>
+          <t>Super + Shift + Alt + 8</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Move window silently to workspace 4</t>
+          <t>Move window silently to workspace 8</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -3078,12 +3042,12 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Super + 5</t>
+          <t>Super + 9</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Switch to workspace 5</t>
+          <t>Switch to workspace 9</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -3110,12 +3074,12 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + 5</t>
+          <t>Super + Shift + 9</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Move window to workspace 5</t>
+          <t>Move window to workspace 9</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -3142,12 +3106,12 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + 5</t>
+          <t>Super + Shift + Alt + 9</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Move window silently to workspace 5</t>
+          <t>Move window silently to workspace 9</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -3174,12 +3138,12 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Super + 6</t>
+          <t>Super + 0</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Switch to workspace 6</t>
+          <t>Switch to workspace 10</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -3206,12 +3170,12 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + 6</t>
+          <t>Super + Shift + 0</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Move window to workspace 6</t>
+          <t>Move window to workspace 10</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -3238,12 +3202,12 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + 6</t>
+          <t>Super + Shift + Alt + 0</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Move window silently to workspace 6</t>
+          <t>Move window silently to workspace 10</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -3270,12 +3234,12 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Super + 7</t>
+          <t>Super + Shift + Left</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Switch to workspace 7</t>
+          <t>Swap window to the left</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -3302,12 +3266,12 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + 7</t>
+          <t>Super + Shift + Right</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Move window to workspace 7</t>
+          <t>Swap window to the right</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -3334,12 +3298,12 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + 7</t>
+          <t>Super + Shift + Up</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Move window silently to workspace 7</t>
+          <t>Swap window up</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -3366,12 +3330,12 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Super + 8</t>
+          <t>Super + Shift + Down</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Switch to workspace 8</t>
+          <t>Swap window down</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -3398,12 +3362,12 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + 8</t>
+          <t>Ctrl + Alt + Tab</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Move window to workspace 8</t>
+          <t>Focus on next monitor</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
@@ -3430,12 +3394,12 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + 8</t>
+          <t>Ctrl + Alt + Shift + Tab</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Move window silently to workspace 8</t>
+          <t>Focus on previous monitor</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -3462,12 +3426,12 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Super + 9</t>
+          <t>Super + -</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Switch to workspace 9</t>
+          <t>Expand window left</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -3494,12 +3458,12 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + 9</t>
+          <t>Super + =</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Move window to workspace 9</t>
+          <t>Shrink window left</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -3526,12 +3490,12 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + 9</t>
+          <t>Super + Shift + -</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Move window silently to workspace 9</t>
+          <t>Shrink window up</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -3558,12 +3522,12 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Super + 0</t>
+          <t>Super + Shift + =</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Switch to workspace 10</t>
+          <t>Expand window down</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -3590,12 +3554,12 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + 0</t>
+          <t>Super + Left-drag</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Move window to workspace 10</t>
+          <t>Move window</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -3622,12 +3586,12 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + 0</t>
+          <t>Super + Right-drag</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Move window silently to workspace 10</t>
+          <t>Resize window</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -3654,17 +3618,17 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Super + S</t>
+          <t>Super + Enter</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Toggle scratchpad</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
@@ -3674,19 +3638,11 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>Replaced by yours</t>
-        </is>
-      </c>
-      <c r="G48" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
-      <c r="H48" s="9" t="inlineStr">
-        <is>
-          <t>Now: Universal save</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="n"/>
+      <c r="H48" s="9" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -3694,17 +3650,17 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + S</t>
+          <t>Super + Shift + B</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Move window to scratchpad</t>
+          <t>Browser</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
@@ -3714,14 +3670,10 @@
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G49" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="n"/>
       <c r="H49" s="9" t="inlineStr"/>
     </row>
     <row r="50">
@@ -3730,17 +3682,17 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Super + Tab</t>
+          <t>Super + Shift + Alt + B</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Next workspace</t>
+          <t>Browser (private)</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
@@ -3750,14 +3702,10 @@
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G50" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="n"/>
       <c r="H50" s="9" t="inlineStr"/>
     </row>
     <row r="51">
@@ -3766,17 +3714,17 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Tab</t>
+          <t>Super + Ctrl + Enter</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Previous workspace</t>
+          <t>Herdr</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -3786,14 +3734,10 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G51" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="n"/>
       <c r="H51" s="9" t="inlineStr"/>
     </row>
     <row r="52">
@@ -3802,17 +3746,17 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + Tab</t>
+          <t>Super + Shift + Alt + M</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Former workspace</t>
+          <t>Music TUI</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
@@ -3822,14 +3766,10 @@
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G52" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G52" s="10" t="n"/>
       <c r="H52" s="9" t="inlineStr"/>
     </row>
     <row r="53">
@@ -3838,17 +3778,17 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + Left</t>
+          <t>Super + Shift + D</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Move workspace to left monitor</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
@@ -3858,14 +3798,10 @@
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G53" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G53" s="10" t="n"/>
       <c r="H53" s="9" t="inlineStr"/>
     </row>
     <row r="54">
@@ -3874,17 +3810,17 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + Right</t>
+          <t>Super + Shift + /</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Move workspace to right monitor</t>
+          <t>Passwords</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
@@ -3894,14 +3830,10 @@
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G54" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G54" s="10" t="n"/>
       <c r="H54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
@@ -3910,17 +3842,17 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + Up</t>
+          <t>Super + Shift + X</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Move workspace to up monitor</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
@@ -3930,14 +3862,10 @@
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G55" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G55" s="10" t="n"/>
       <c r="H55" s="9" t="inlineStr"/>
     </row>
     <row r="56">
@@ -3946,17 +3874,17 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + Down</t>
+          <t>Super + Shift + Alt + X</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Move workspace to down monitor</t>
+          <t>X Post</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
@@ -3966,14 +3894,10 @@
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G56" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="n"/>
       <c r="H56" s="9" t="inlineStr"/>
     </row>
     <row r="57">
@@ -3982,17 +3906,17 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Left</t>
+          <t>Super + Space</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Swap window to the left</t>
+          <t>Omarchy menu</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
@@ -4014,17 +3938,17 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Right</t>
+          <t>Super + Ctrl + E</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Swap window to the right</t>
+          <t>Emojis</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
@@ -4046,17 +3970,17 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Up</t>
+          <t>Super + Ctrl + O</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Swap window up</t>
+          <t>Toggle menu</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
@@ -4078,17 +4002,17 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Down</t>
+          <t>Super + Esc</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Swap window down</t>
+          <t>System menu</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
@@ -4110,17 +4034,17 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Alt + Tab</t>
+          <t>Super + K</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Focus on next window; Reveal active window on top</t>
+          <t>Keybindings</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
@@ -4130,19 +4054,11 @@
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G61" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
-      <c r="H61" s="9" t="inlineStr">
-        <is>
-          <t>I want to force myself towards using the vim type bindings</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="9" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -4150,17 +4066,17 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Alt + Shift + Tab</t>
+          <t>Super + Ctrl + K</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Focus on previous window; Reveal active window on top</t>
+          <t>Herdr keybindings</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
@@ -4170,14 +4086,10 @@
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G62" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="n"/>
       <c r="H62" s="9" t="inlineStr"/>
     </row>
     <row r="63">
@@ -4186,17 +4098,17 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>Ctrl + Alt + Tab</t>
+          <t>Super + Ctrl + Space</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Focus on next monitor</t>
+          <t>Background switcher</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
@@ -4218,17 +4130,17 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Ctrl + Alt + Shift + Tab</t>
+          <t>Super + Shift + Ctrl + Space</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Focus on previous monitor</t>
+          <t>Theme menu</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
@@ -4250,17 +4162,17 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Super + -</t>
+          <t>Super + Alt + ,</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Expand window left</t>
+          <t>Invoke last notification</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
@@ -4282,17 +4194,17 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Super + =</t>
+          <t>Super + Shift + Ctrl + A</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Shrink window left</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
@@ -4314,17 +4226,17 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + -</t>
+          <t>Super + Ctrl + T</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Shrink window up</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
@@ -4346,17 +4258,17 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + =</t>
+          <t>Super + Ctrl + L</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Expand window down</t>
+          <t>Lock system</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
@@ -4378,17 +4290,17 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + -</t>
+          <t>Super + C</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Expand window left a little</t>
+          <t>Universal copy</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Clipboard</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
@@ -4398,14 +4310,10 @@
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G69" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G69" s="10" t="n"/>
       <c r="H69" s="9" t="inlineStr"/>
     </row>
     <row r="70">
@@ -4414,17 +4322,17 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + =</t>
+          <t>Super + V</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Shrink window left a little</t>
+          <t>Universal paste</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Clipboard</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
@@ -4434,14 +4342,10 @@
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G70" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G70" s="10" t="n"/>
       <c r="H70" s="9" t="inlineStr"/>
     </row>
     <row r="71">
@@ -4450,17 +4354,17 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + -</t>
+          <t>Super + X</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Shrink window up a little</t>
+          <t>Universal cut</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Clipboard</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -4470,14 +4374,10 @@
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G71" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G71" s="10" t="n"/>
       <c r="H71" s="9" t="inlineStr"/>
     </row>
     <row r="72">
@@ -4486,17 +4386,17 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + =</t>
+          <t>Super + Ctrl + X</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Expand window down a little</t>
+          <t>Toggle dictation</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Dictation</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
@@ -4506,14 +4406,10 @@
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G72" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G72" s="10" t="n"/>
       <c r="H72" s="9" t="inlineStr"/>
     </row>
     <row r="73">
@@ -4522,34 +4418,30 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + -</t>
+          <t>Super + Q</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Expand window left a lot</t>
+          <t>Close window</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Yours</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>Omarchy</t>
+          <t>You</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G73" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G73" s="10" t="n"/>
       <c r="H73" s="9" t="inlineStr"/>
     </row>
     <row r="74">
@@ -4558,34 +4450,30 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + =</t>
+          <t>Super + A</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Shrink window left a lot</t>
+          <t>Universal select all</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Yours</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>Omarchy</t>
+          <t>You</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G74" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="n"/>
       <c r="H74" s="9" t="inlineStr"/>
     </row>
     <row r="75">
@@ -4594,35 +4482,35 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + Shift + -</t>
+          <t>Super + S</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Shrink window up a lot</t>
+          <t>Universal save</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Yours</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>Omarchy</t>
+          <t>You</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G75" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
-      <c r="H75" s="9" t="inlineStr"/>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="n"/>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>Replaces an Omarchy default</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -4630,35 +4518,35 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + Shift + =</t>
+          <t>Super + Shift + F</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Expand window down a lot</t>
+          <t>File manager (cwd)</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Yours</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>Omarchy</t>
+          <t>You</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G76" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
-      <c r="H76" s="9" t="inlineStr"/>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="n"/>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>Replaces an Omarchy default</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -4666,35 +4554,35 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>Super + Scroll down</t>
+          <t>Super + ,</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Scroll active workspace forward</t>
+          <t>Dismiss all notifications</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Yours</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>Omarchy</t>
+          <t>You</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G77" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
-      <c r="H77" s="9" t="inlineStr"/>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G77" s="10" t="n"/>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>Replaces an Omarchy default</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -4702,35 +4590,35 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Super + Scroll up</t>
+          <t>Super + Ctrl + 4</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Scroll active workspace backward</t>
+          <t>Screenshot</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Yours</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>Omarchy</t>
+          <t>You</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G78" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
-      <c r="H78" s="9" t="inlineStr"/>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G78" s="10" t="n"/>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>Replaces an Omarchy default</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
@@ -4738,22 +4626,22 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Super + Left-drag</t>
+          <t>Super + Ctrl + 5</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Move window</t>
+          <t>Screenrecording</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Yours</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>Omarchy</t>
+          <t>You</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
@@ -4762,7 +4650,11 @@
         </is>
       </c>
       <c r="G79" s="10" t="n"/>
-      <c r="H79" s="9" t="inlineStr"/>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>Replaces an Omarchy default</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
@@ -4770,22 +4662,22 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Super + Right-drag</t>
+          <t>Super + Ctrl + 6</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Resize window</t>
+          <t>Color picker</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Yours</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>Omarchy</t>
+          <t>You</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
@@ -4794,7 +4686,11 @@
         </is>
       </c>
       <c r="G80" s="10" t="n"/>
-      <c r="H80" s="9" t="inlineStr"/>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>Replaces an Omarchy default</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
@@ -4802,35 +4698,35 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>Super + G</t>
+          <t>Super + Shift + M</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Toggle window grouping</t>
+          <t>Apple Music</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Yours</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>Omarchy</t>
+          <t>You</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G81" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
-      <c r="H81" s="9" t="inlineStr"/>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G81" s="10" t="n"/>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>Replaces an Omarchy default</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
@@ -4838,17 +4734,17 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + G</t>
+          <t>PowerOff key</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Move active window out of group</t>
+          <t>Power menu</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
@@ -4858,14 +4754,10 @@
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G82" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="n"/>
       <c r="H82" s="9" t="inlineStr"/>
     </row>
     <row r="83">
@@ -4874,17 +4766,17 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + Left</t>
+          <t>Laptop lid closed</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Move window to group on left</t>
+          <t>Runs omarchy-system-lid-close</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
@@ -4894,14 +4786,10 @@
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G83" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="n"/>
       <c r="H83" s="9" t="inlineStr"/>
     </row>
     <row r="84">
@@ -4910,17 +4798,17 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + Right</t>
+          <t>Laptop lid opened</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Move window to group on right</t>
+          <t>Runs omarchy-hyprland-monitor-clamshell</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
@@ -4930,14 +4818,10 @@
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G84" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G84" s="10" t="n"/>
       <c r="H84" s="9" t="inlineStr"/>
     </row>
     <row r="85">
@@ -4946,17 +4830,17 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + Up</t>
+          <t>AudioRaiseVolume key</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Move window to group on top</t>
+          <t>Volume up</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
@@ -4966,14 +4850,10 @@
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G85" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G85" s="10" t="n"/>
       <c r="H85" s="9" t="inlineStr"/>
     </row>
     <row r="86">
@@ -4982,17 +4862,17 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + Down</t>
+          <t>AudioLowerVolume key</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Move window to group on bottom</t>
+          <t>Volume down</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
@@ -5002,14 +4882,10 @@
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G86" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G86" s="10" t="n"/>
       <c r="H86" s="9" t="inlineStr"/>
     </row>
     <row r="87">
@@ -5018,17 +4894,17 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + Tab</t>
+          <t>AudioMute key</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Next window in group</t>
+          <t>Mute</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
@@ -5038,14 +4914,10 @@
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G87" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G87" s="10" t="n"/>
       <c r="H87" s="9" t="inlineStr"/>
     </row>
     <row r="88">
@@ -5054,17 +4926,17 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + Shift + Tab</t>
+          <t>AudioMicMute key</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Previous window in group</t>
+          <t>Mute microphone</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
@@ -5074,14 +4946,10 @@
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G88" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="n"/>
       <c r="H88" s="9" t="inlineStr"/>
     </row>
     <row r="89">
@@ -5090,17 +4958,17 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + Left</t>
+          <t>Alt + AudioRaiseVolume key</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Move grouped window focus left</t>
+          <t>Volume up precise</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
@@ -5110,14 +4978,10 @@
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G89" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="n"/>
       <c r="H89" s="9" t="inlineStr"/>
     </row>
     <row r="90">
@@ -5126,17 +4990,17 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + Right</t>
+          <t>Alt + AudioLowerVolume key</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Move grouped window focus right</t>
+          <t>Volume down precise</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
@@ -5146,14 +5010,10 @@
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G90" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G90" s="10" t="n"/>
       <c r="H90" s="9" t="inlineStr"/>
     </row>
     <row r="91">
@@ -5162,35 +5022,35 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + Scroll down</t>
+          <t>MonBrightnessUp key</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Next window in group</t>
+          <t>Brightness up</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Yours</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>Omarchy</t>
+          <t>You</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G91" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
-      <c r="H91" s="9" t="inlineStr"/>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G91" s="10" t="n"/>
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>Replaces an Omarchy default</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
@@ -5198,35 +5058,35 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + Scroll up</t>
+          <t>MonBrightnessDown key</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Previous window in group</t>
+          <t>Brightness down</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Yours</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>Omarchy</t>
+          <t>You</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G92" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
-      <c r="H92" s="9" t="inlineStr"/>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G92" s="10" t="n"/>
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>Replaces an Omarchy default</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
@@ -5234,35 +5094,35 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + 1</t>
+          <t>Shift + MonBrightnessUp key</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Switch to group window 1</t>
+          <t>Brightness maximum</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Yours</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>Omarchy</t>
+          <t>You</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G93" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
-      <c r="H93" s="9" t="inlineStr"/>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G93" s="10" t="n"/>
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>Replaces an Omarchy default</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
@@ -5270,35 +5130,35 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + 2</t>
+          <t>Shift + MonBrightnessDown key</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Switch to group window 2</t>
+          <t>Brightness minimum</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Yours</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>Omarchy</t>
+          <t>You</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G94" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
-      <c r="H94" s="9" t="inlineStr"/>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G94" s="10" t="n"/>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>Replaces an Omarchy default</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
@@ -5306,35 +5166,35 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + 3</t>
+          <t>Alt + MonBrightnessUp key</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>Switch to group window 3</t>
+          <t>Brightness up precise</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Yours</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>Omarchy</t>
+          <t>You</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G95" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
-      <c r="H95" s="9" t="inlineStr"/>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="n"/>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>Replaces an Omarchy default</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
@@ -5342,35 +5202,35 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + 4</t>
+          <t>Alt + MonBrightnessDown key</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Switch to group window 4</t>
+          <t>Brightness down precise</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Windows &amp; workspaces</t>
+          <t>Yours</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>Omarchy</t>
+          <t>You</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G96" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
-      <c r="H96" s="9" t="inlineStr"/>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="n"/>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>Replaces an Omarchy default</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
@@ -5378,12 +5238,12 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + 5</t>
+          <t>Super + W</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Switch to group window 5</t>
+          <t>Close window</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
@@ -5401,11 +5261,7 @@
           <t>Removed by you</t>
         </is>
       </c>
-      <c r="G97" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+      <c r="G97" s="10" t="n"/>
       <c r="H97" s="9" t="inlineStr"/>
     </row>
     <row r="98">
@@ -5414,12 +5270,12 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Super + /</t>
+          <t>Ctrl + Alt + Delete</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Monitor scaling up</t>
+          <t>Close all windows</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
@@ -5450,12 +5306,12 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + /</t>
+          <t>Super + J</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Monitor scaling down</t>
+          <t>Toggle window split</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
@@ -5486,17 +5342,17 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Super + Enter</t>
+          <t>Super + P</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pseudo window</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
@@ -5506,10 +5362,14 @@
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G100" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G100" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H100" s="9" t="inlineStr"/>
     </row>
     <row r="101">
@@ -5518,17 +5378,17 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Enter</t>
+          <t>Super + T</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Browser</t>
+          <t>Toggle window floating/tiling</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -5541,11 +5401,7 @@
           <t>Removed by you</t>
         </is>
       </c>
-      <c r="G101" s="10" t="inlineStr">
-        <is>
-          <t>Remove</t>
-        </is>
-      </c>
+      <c r="G101" s="10" t="n"/>
       <c r="H101" s="9" t="inlineStr"/>
     </row>
     <row r="102">
@@ -5554,17 +5410,17 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + F</t>
+          <t>Super + F</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>File manager</t>
+          <t>Full screen</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
@@ -5574,19 +5430,11 @@
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>Replaced by yours</t>
-        </is>
-      </c>
-      <c r="G102" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
-      <c r="H102" s="9" t="inlineStr">
-        <is>
-          <t>Now: File manager (cwd)</t>
-        </is>
-      </c>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G102" s="10" t="n"/>
+      <c r="H102" s="9" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n">
@@ -5594,17 +5442,17 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + Shift + F</t>
+          <t>Super + Ctrl + F</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>File manager (cwd)</t>
+          <t>Tiled full screen</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
@@ -5619,14 +5467,10 @@
       </c>
       <c r="G103" s="10" t="inlineStr">
         <is>
-          <t>rebind</t>
-        </is>
-      </c>
-      <c r="H103" s="9" t="inlineStr">
-        <is>
-          <t>super+shift+f</t>
-        </is>
-      </c>
+          <t>remove</t>
+        </is>
+      </c>
+      <c r="H103" s="9" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
@@ -5634,17 +5478,17 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + B</t>
+          <t>Super + Alt + F</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>Browser</t>
+          <t>Full width</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
@@ -5654,10 +5498,14 @@
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G104" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G104" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H104" s="9" t="inlineStr"/>
     </row>
     <row r="105">
@@ -5666,17 +5514,17 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + B</t>
+          <t>Super + O</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>Browser (private)</t>
+          <t>Pop window out (float &amp; pin)</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
@@ -5686,10 +5534,14 @@
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G105" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G105" s="10" t="inlineStr">
+        <is>
+          <t>Remove</t>
+        </is>
+      </c>
       <c r="H105" s="9" t="inlineStr"/>
     </row>
     <row r="106">
@@ -5698,17 +5550,17 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + N</t>
+          <t>Super + Alt + Home</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Editor</t>
+          <t>Save window width</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
@@ -5723,7 +5575,7 @@
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="H106" s="9" t="inlineStr"/>
@@ -5734,17 +5586,17 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + Enter</t>
+          <t>Super + Home</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>Tmux</t>
+          <t>Restore window width</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
@@ -5762,11 +5614,7 @@
           <t>Remove</t>
         </is>
       </c>
-      <c r="H107" s="9" t="inlineStr">
-        <is>
-          <t>remove tmux</t>
-        </is>
-      </c>
+      <c r="H107" s="9" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
@@ -5774,17 +5622,17 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + Enter</t>
+          <t>Super + L</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Herdr</t>
+          <t>Toggle workspace layout</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
@@ -5794,10 +5642,14 @@
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G108" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G108" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H108" s="9" t="inlineStr"/>
     </row>
     <row r="109">
@@ -5806,17 +5658,17 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + M</t>
+          <t>Super + S</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>Music</t>
+          <t>Toggle scratchpad</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
@@ -5829,10 +5681,14 @@
           <t>Replaced by yours</t>
         </is>
       </c>
-      <c r="G109" s="10" t="n"/>
+      <c r="G109" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H109" s="9" t="inlineStr">
         <is>
-          <t>Now: Apple Music</t>
+          <t>Now: Universal save</t>
         </is>
       </c>
     </row>
@@ -5842,17 +5698,17 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + M</t>
+          <t>Super + Alt + S</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Music TUI</t>
+          <t>Move window to scratchpad</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
@@ -5862,10 +5718,14 @@
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G110" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G110" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H110" s="9" t="inlineStr"/>
     </row>
     <row r="111">
@@ -5874,17 +5734,17 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + D</t>
+          <t>Super + Tab</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>Next workspace</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
@@ -5894,10 +5754,14 @@
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G111" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G111" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H111" s="9" t="inlineStr"/>
     </row>
     <row r="112">
@@ -5906,17 +5770,17 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + G</t>
+          <t>Super + Shift + Tab</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>Signal</t>
+          <t>Previous workspace</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
@@ -5931,7 +5795,7 @@
       </c>
       <c r="G112" s="10" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="H112" s="9" t="inlineStr"/>
@@ -5942,17 +5806,17 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + O</t>
+          <t>Super + Ctrl + Tab</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>Obsidian</t>
+          <t>Former workspace</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
@@ -5967,7 +5831,7 @@
       </c>
       <c r="G113" s="10" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="H113" s="9" t="inlineStr"/>
@@ -5978,17 +5842,17 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + W</t>
+          <t>Super + Shift + Alt + Left</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Omawrite</t>
+          <t>Move workspace to left monitor</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
@@ -6003,7 +5867,7 @@
       </c>
       <c r="G114" s="10" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="H114" s="9" t="inlineStr"/>
@@ -6014,17 +5878,17 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + /</t>
+          <t>Super + Shift + Alt + Right</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Passwords</t>
+          <t>Move workspace to right monitor</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
@@ -6034,10 +5898,14 @@
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G115" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G115" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H115" s="9" t="inlineStr"/>
     </row>
     <row r="116">
@@ -6046,17 +5914,17 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + A</t>
+          <t>Super + Shift + Alt + Up</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Move workspace to up monitor</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
@@ -6071,7 +5939,7 @@
       </c>
       <c r="G116" s="10" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="H116" s="9" t="inlineStr"/>
@@ -6082,17 +5950,17 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + A</t>
+          <t>Super + Shift + Alt + Down</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Grok</t>
+          <t>Move workspace to down monitor</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
@@ -6107,7 +5975,7 @@
       </c>
       <c r="G117" s="10" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="H117" s="9" t="inlineStr"/>
@@ -6118,17 +5986,17 @@
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + C</t>
+          <t>Alt + Tab</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Focus on next window; Reveal active window on top</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
@@ -6143,10 +6011,14 @@
       </c>
       <c r="G118" s="10" t="inlineStr">
         <is>
-          <t>Remove</t>
-        </is>
-      </c>
-      <c r="H118" s="9" t="inlineStr"/>
+          <t>remove</t>
+        </is>
+      </c>
+      <c r="H118" s="9" t="inlineStr">
+        <is>
+          <t>I want to force myself towards using the vim type bindings</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="n">
@@ -6154,17 +6026,17 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + E</t>
+          <t>Alt + Shift + Tab</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Focus on previous window; Reveal active window on top</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
@@ -6179,7 +6051,7 @@
       </c>
       <c r="G119" s="10" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="H119" s="9" t="inlineStr"/>
@@ -6190,17 +6062,17 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + E</t>
+          <t>Super + Alt + -</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>New email</t>
+          <t>Expand window left a little</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
@@ -6215,7 +6087,7 @@
       </c>
       <c r="G120" s="10" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="H120" s="9" t="inlineStr"/>
@@ -6226,17 +6098,17 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Y</t>
+          <t>Super + Alt + =</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Shrink window left a little</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
@@ -6251,7 +6123,7 @@
       </c>
       <c r="G121" s="10" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="H121" s="9" t="inlineStr"/>
@@ -6262,17 +6134,17 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + G</t>
+          <t>Super + Shift + Alt + -</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Shrink window up a little</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr">
@@ -6287,7 +6159,7 @@
       </c>
       <c r="G122" s="10" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="H122" s="9" t="inlineStr"/>
@@ -6298,17 +6170,17 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Ctrl + G</t>
+          <t>Super + Shift + Alt + =</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Google Messages</t>
+          <t>Expand window down a little</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr">
@@ -6323,7 +6195,7 @@
       </c>
       <c r="G123" s="10" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="H123" s="9" t="inlineStr"/>
@@ -6334,17 +6206,17 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + P</t>
+          <t>Super + Ctrl + -</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>Google Photos</t>
+          <t>Expand window left a lot</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr">
@@ -6359,7 +6231,7 @@
       </c>
       <c r="G124" s="10" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="H124" s="9" t="inlineStr"/>
@@ -6370,17 +6242,17 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + S</t>
+          <t>Super + Ctrl + =</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>Shrink window left a lot</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr">
@@ -6393,7 +6265,11 @@
           <t>Removed by you</t>
         </is>
       </c>
-      <c r="G125" s="10" t="n"/>
+      <c r="G125" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H125" s="9" t="inlineStr"/>
     </row>
     <row r="126">
@@ -6402,17 +6278,17 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + X</t>
+          <t>Super + Ctrl + Shift + -</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Shrink window up a lot</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr">
@@ -6422,10 +6298,14 @@
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G126" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G126" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H126" s="9" t="inlineStr"/>
     </row>
     <row r="127">
@@ -6434,17 +6314,17 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + X</t>
+          <t>Super + Ctrl + Shift + =</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>X Post</t>
+          <t>Expand window down a lot</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr">
@@ -6454,10 +6334,14 @@
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G127" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G127" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H127" s="9" t="inlineStr"/>
     </row>
     <row r="128">
@@ -6466,17 +6350,17 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>Super + Space</t>
+          <t>Super + Scroll down</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>Omarchy menu</t>
+          <t>Scroll active workspace forward</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E128" s="7" t="inlineStr">
@@ -6486,10 +6370,14 @@
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G128" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G128" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H128" s="9" t="inlineStr"/>
     </row>
     <row r="129">
@@ -6498,17 +6386,17 @@
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + Space</t>
+          <t>Super + Scroll up</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Apps menu</t>
+          <t>Scroll active workspace backward</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr">
@@ -6526,11 +6414,7 @@
           <t>remove</t>
         </is>
       </c>
-      <c r="H129" s="9" t="inlineStr">
-        <is>
-          <t>I use super+space for looking for apps</t>
-        </is>
-      </c>
+      <c r="H129" s="9" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="7" t="n">
@@ -6538,17 +6422,17 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + E</t>
+          <t>Super + G</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>Emojis</t>
+          <t>Toggle window grouping</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr">
@@ -6558,10 +6442,14 @@
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G130" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G130" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H130" s="9" t="inlineStr"/>
     </row>
     <row r="131">
@@ -6570,17 +6458,17 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + C</t>
+          <t>Super + Alt + G</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Capture menu</t>
+          <t>Move active window out of group</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E131" s="7" t="inlineStr">
@@ -6595,7 +6483,7 @@
       </c>
       <c r="G131" s="10" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="H131" s="9" t="inlineStr"/>
@@ -6606,17 +6494,17 @@
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + O</t>
+          <t>Super + Alt + Left</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>Toggle menu</t>
+          <t>Move window to group on left</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E132" s="7" t="inlineStr">
@@ -6626,10 +6514,14 @@
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G132" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G132" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H132" s="9" t="inlineStr"/>
     </row>
     <row r="133">
@@ -6638,17 +6530,17 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + H</t>
+          <t>Super + Alt + Right</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>Hardware menu</t>
+          <t>Move window to group on right</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr">
@@ -6663,14 +6555,10 @@
       </c>
       <c r="G133" s="10" t="inlineStr">
         <is>
-          <t>Remove</t>
-        </is>
-      </c>
-      <c r="H133" s="9" t="inlineStr">
-        <is>
-          <t>Doesn't seem  to do anything for me.</t>
-        </is>
-      </c>
+          <t>remove</t>
+        </is>
+      </c>
+      <c r="H133" s="9" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="7" t="n">
@@ -6678,17 +6566,17 @@
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + code:201</t>
+          <t>Super + Alt + Up</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>Omarchy menu</t>
+          <t>Move window to group on top</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr">
@@ -6703,7 +6591,7 @@
       </c>
       <c r="G134" s="10" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="H134" s="9" t="inlineStr"/>
@@ -6714,17 +6602,17 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>Super + Esc</t>
+          <t>Super + Alt + Down</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>System menu</t>
+          <t>Move window to group on bottom</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr">
@@ -6734,10 +6622,14 @@
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G135" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G135" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H135" s="9" t="inlineStr"/>
     </row>
     <row r="136">
@@ -6746,17 +6638,17 @@
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>PowerOff key</t>
+          <t>Super + Alt + Tab</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>Power menu</t>
+          <t>Next window in group</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E136" s="7" t="inlineStr">
@@ -6766,10 +6658,14 @@
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G136" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G136" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H136" s="9" t="inlineStr"/>
     </row>
     <row r="137">
@@ -6778,17 +6674,17 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>Super + K</t>
+          <t>Super + Alt + Shift + Tab</t>
         </is>
       </c>
       <c r="C137" s="9" t="inlineStr">
         <is>
-          <t>Keybindings</t>
+          <t>Previous window in group</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E137" s="7" t="inlineStr">
@@ -6798,10 +6694,14 @@
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G137" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G137" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H137" s="9" t="inlineStr"/>
     </row>
     <row r="138">
@@ -6810,17 +6710,17 @@
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + K</t>
+          <t>Super + Ctrl + Left</t>
         </is>
       </c>
       <c r="C138" s="9" t="inlineStr">
         <is>
-          <t>Tmux keybindings</t>
+          <t>Move grouped window focus left</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E138" s="7" t="inlineStr">
@@ -6835,7 +6735,7 @@
       </c>
       <c r="G138" s="10" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="H138" s="9" t="inlineStr"/>
@@ -6846,17 +6746,17 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + K</t>
+          <t>Super + Ctrl + Right</t>
         </is>
       </c>
       <c r="C139" s="9" t="inlineStr">
         <is>
-          <t>Herdr keybindings</t>
+          <t>Move grouped window focus right</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr">
@@ -6866,10 +6766,14 @@
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G139" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G139" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H139" s="9" t="inlineStr"/>
     </row>
     <row r="140">
@@ -6878,17 +6782,17 @@
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + Q</t>
+          <t>Super + Alt + Scroll down</t>
         </is>
       </c>
       <c r="C140" s="9" t="inlineStr">
         <is>
-          <t>Calculator</t>
+          <t>Next window in group</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E140" s="7" t="inlineStr">
@@ -6914,17 +6818,17 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>Calculator key</t>
+          <t>Super + Alt + Scroll up</t>
         </is>
       </c>
       <c r="C141" s="9" t="inlineStr">
         <is>
-          <t>Calculator</t>
+          <t>Previous window in group</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E141" s="7" t="inlineStr">
@@ -6950,17 +6854,17 @@
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Space</t>
+          <t>Super + Alt + 1</t>
         </is>
       </c>
       <c r="C142" s="9" t="inlineStr">
         <is>
-          <t>Toggle top bar</t>
+          <t>Switch to group window 1</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E142" s="7" t="inlineStr">
@@ -6986,17 +6890,17 @@
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + Space</t>
+          <t>Super + Alt + 2</t>
         </is>
       </c>
       <c r="C143" s="9" t="inlineStr">
         <is>
-          <t>Background switcher</t>
+          <t>Switch to group window 2</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E143" s="7" t="inlineStr">
@@ -7006,10 +6910,14 @@
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G143" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G143" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H143" s="9" t="inlineStr"/>
     </row>
     <row r="144">
@@ -7018,17 +6926,17 @@
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Ctrl + Space</t>
+          <t>Super + Alt + 3</t>
         </is>
       </c>
       <c r="C144" s="9" t="inlineStr">
         <is>
-          <t>Theme menu</t>
+          <t>Switch to group window 3</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E144" s="7" t="inlineStr">
@@ -7038,10 +6946,14 @@
       </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G144" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G144" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H144" s="9" t="inlineStr"/>
     </row>
     <row r="145">
@@ -7050,17 +6962,17 @@
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>Super + Backspace</t>
+          <t>Super + Alt + 4</t>
         </is>
       </c>
       <c r="C145" s="9" t="inlineStr">
         <is>
-          <t>Toggle window transparency</t>
+          <t>Switch to group window 4</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E145" s="7" t="inlineStr">
@@ -7078,11 +6990,7 @@
           <t>remove</t>
         </is>
       </c>
-      <c r="H145" s="9" t="inlineStr">
-        <is>
-          <t>Make sure we have transparentcy turned off first.</t>
-        </is>
-      </c>
+      <c r="H145" s="9" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n">
@@ -7090,17 +6998,17 @@
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Backspace</t>
+          <t>Super + Alt + 5</t>
         </is>
       </c>
       <c r="C146" s="9" t="inlineStr">
         <is>
-          <t>Toggle window gaps</t>
+          <t>Switch to group window 5</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E146" s="7" t="inlineStr">
@@ -7113,7 +7021,11 @@
           <t>Removed by you</t>
         </is>
       </c>
-      <c r="G146" s="10" t="n"/>
+      <c r="G146" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H146" s="9" t="inlineStr"/>
     </row>
     <row r="147">
@@ -7122,17 +7034,17 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + Backspace</t>
+          <t>Super + /</t>
         </is>
       </c>
       <c r="C147" s="9" t="inlineStr">
         <is>
-          <t>Toggle single-window square aspect</t>
+          <t>Monitor scaling up</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E147" s="7" t="inlineStr">
@@ -7158,17 +7070,17 @@
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>Super + ,</t>
+          <t>Super + Alt + /</t>
         </is>
       </c>
       <c r="C148" s="9" t="inlineStr">
         <is>
-          <t>Dismiss last notification</t>
+          <t>Monitor scaling down</t>
         </is>
       </c>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Windows &amp; workspaces</t>
         </is>
       </c>
       <c r="E148" s="7" t="inlineStr">
@@ -7178,19 +7090,15 @@
       </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
-          <t>Replaced by yours</t>
+          <t>Removed by you</t>
         </is>
       </c>
       <c r="G148" s="10" t="inlineStr">
         <is>
-          <t>rebind</t>
-        </is>
-      </c>
-      <c r="H148" s="9" t="inlineStr">
-        <is>
-          <t>Now: Dismiss all notifications</t>
-        </is>
-      </c>
+          <t>remove</t>
+        </is>
+      </c>
+      <c r="H148" s="9" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="7" t="n">
@@ -7198,17 +7106,17 @@
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + ,</t>
+          <t>Super + Shift + Enter</t>
         </is>
       </c>
       <c r="C149" s="9" t="inlineStr">
         <is>
-          <t>Dismiss all notifications</t>
+          <t>Browser</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E149" s="7" t="inlineStr">
@@ -7223,7 +7131,7 @@
       </c>
       <c r="G149" s="10" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="H149" s="9" t="inlineStr"/>
@@ -7234,17 +7142,17 @@
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + ,</t>
+          <t>Super + Shift + F</t>
         </is>
       </c>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>Toggle silencing notifications</t>
+          <t>File manager</t>
         </is>
       </c>
       <c r="D150" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr">
@@ -7254,7 +7162,7 @@
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
+          <t>Replaced by yours</t>
         </is>
       </c>
       <c r="G150" s="10" t="inlineStr">
@@ -7262,7 +7170,11 @@
           <t>remove</t>
         </is>
       </c>
-      <c r="H150" s="9" t="inlineStr"/>
+      <c r="H150" s="9" t="inlineStr">
+        <is>
+          <t>Now: File manager (cwd)</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="7" t="n">
@@ -7270,17 +7182,17 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + ,</t>
+          <t>Super + Alt + Shift + F</t>
         </is>
       </c>
       <c r="C151" s="9" t="inlineStr">
         <is>
-          <t>Invoke last notification</t>
+          <t>File manager (cwd)</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E151" s="7" t="inlineStr">
@@ -7290,11 +7202,19 @@
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G151" s="10" t="n"/>
-      <c r="H151" s="9" t="inlineStr"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G151" s="10" t="inlineStr">
+        <is>
+          <t>rebind</t>
+        </is>
+      </c>
+      <c r="H151" s="9" t="inlineStr">
+        <is>
+          <t>super+shift+f</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="7" t="n">
@@ -7302,17 +7222,17 @@
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Alt + ,</t>
+          <t>Super + Shift + N</t>
         </is>
       </c>
       <c r="C152" s="9" t="inlineStr">
         <is>
-          <t>Open notification history</t>
+          <t>Editor</t>
         </is>
       </c>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr">
@@ -7338,17 +7258,17 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + I</t>
+          <t>Super + Alt + Enter</t>
         </is>
       </c>
       <c r="C153" s="9" t="inlineStr">
         <is>
-          <t>Toggle locking on idle</t>
+          <t>Tmux</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr">
@@ -7363,10 +7283,14 @@
       </c>
       <c r="G153" s="10" t="inlineStr">
         <is>
-          <t>remove</t>
-        </is>
-      </c>
-      <c r="H153" s="9" t="inlineStr"/>
+          <t>Remove</t>
+        </is>
+      </c>
+      <c r="H153" s="9" t="inlineStr">
+        <is>
+          <t>remove tmux</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="7" t="n">
@@ -7374,17 +7298,17 @@
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + N</t>
+          <t>Super + Shift + M</t>
         </is>
       </c>
       <c r="C154" s="9" t="inlineStr">
         <is>
-          <t>Toggle nightlight</t>
+          <t>Music</t>
         </is>
       </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr">
@@ -7394,15 +7318,15 @@
       </c>
       <c r="F154" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G154" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
-      <c r="H154" s="9" t="inlineStr"/>
+          <t>Replaced by yours</t>
+        </is>
+      </c>
+      <c r="G154" s="10" t="n"/>
+      <c r="H154" s="9" t="inlineStr">
+        <is>
+          <t>Now: Apple Music</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="7" t="n">
@@ -7410,17 +7334,17 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + Delete</t>
+          <t>Super + Shift + G</t>
         </is>
       </c>
       <c r="C155" s="9" t="inlineStr">
         <is>
-          <t>Toggle laptop display</t>
+          <t>Signal</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E155" s="7" t="inlineStr">
@@ -7435,7 +7359,7 @@
       </c>
       <c r="G155" s="10" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="H155" s="9" t="inlineStr"/>
@@ -7446,17 +7370,17 @@
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + Alt + Delete</t>
+          <t>Super + Shift + O</t>
         </is>
       </c>
       <c r="C156" s="9" t="inlineStr">
         <is>
-          <t>Toggle laptop display mirroring</t>
+          <t>Obsidian</t>
         </is>
       </c>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr">
@@ -7471,7 +7395,7 @@
       </c>
       <c r="G156" s="10" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="H156" s="9" t="inlineStr"/>
@@ -7482,13 +7406,17 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>switch:on:Lid Switch</t>
-        </is>
-      </c>
-      <c r="C157" s="9" t="inlineStr"/>
+          <t>Super + Shift + W</t>
+        </is>
+      </c>
+      <c r="C157" s="9" t="inlineStr">
+        <is>
+          <t>Omawrite</t>
+        </is>
+      </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E157" s="7" t="inlineStr">
@@ -7498,10 +7426,14 @@
       </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G157" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G157" s="10" t="inlineStr">
+        <is>
+          <t>Remove</t>
+        </is>
+      </c>
       <c r="H157" s="9" t="inlineStr"/>
     </row>
     <row r="158">
@@ -7510,13 +7442,17 @@
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>switch:off:Lid Switch</t>
-        </is>
-      </c>
-      <c r="C158" s="9" t="inlineStr"/>
+          <t>Super + Shift + A</t>
+        </is>
+      </c>
+      <c r="C158" s="9" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E158" s="7" t="inlineStr">
@@ -7526,10 +7462,14 @@
       </c>
       <c r="F158" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G158" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G158" s="10" t="inlineStr">
+        <is>
+          <t>Remove</t>
+        </is>
+      </c>
       <c r="H158" s="9" t="inlineStr"/>
     </row>
     <row r="159">
@@ -7538,17 +7478,17 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>Print Screen</t>
+          <t>Super + Shift + Alt + A</t>
         </is>
       </c>
       <c r="C159" s="9" t="inlineStr">
         <is>
-          <t>Screenshot</t>
+          <t>Grok</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E159" s="7" t="inlineStr">
@@ -7563,7 +7503,7 @@
       </c>
       <c r="G159" s="10" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="H159" s="9" t="inlineStr"/>
@@ -7574,17 +7514,17 @@
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>Alt + Print Screen</t>
+          <t>Super + Shift + C</t>
         </is>
       </c>
       <c r="C160" s="9" t="inlineStr">
         <is>
-          <t>Screenrecording</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E160" s="7" t="inlineStr">
@@ -7599,14 +7539,10 @@
       </c>
       <c r="G160" s="10" t="inlineStr">
         <is>
-          <t>rebind</t>
-        </is>
-      </c>
-      <c r="H160" s="9" t="inlineStr">
-        <is>
-          <t>super+ctrl+5</t>
-        </is>
-      </c>
+          <t>Remove</t>
+        </is>
+      </c>
+      <c r="H160" s="9" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="n">
@@ -7614,17 +7550,17 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + code:34</t>
+          <t>Super + Shift + E</t>
         </is>
       </c>
       <c r="C161" s="9" t="inlineStr">
         <is>
-          <t>Make webcam overlay smaller</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E161" s="7" t="inlineStr">
@@ -7639,7 +7575,7 @@
       </c>
       <c r="G161" s="10" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="H161" s="9" t="inlineStr"/>
@@ -7650,17 +7586,17 @@
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>Super + Alt + code:35</t>
+          <t>Super + Shift + Alt + E</t>
         </is>
       </c>
       <c r="C162" s="9" t="inlineStr">
         <is>
-          <t>Make webcam overlay larger</t>
+          <t>New email</t>
         </is>
       </c>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E162" s="7" t="inlineStr">
@@ -7675,7 +7611,7 @@
       </c>
       <c r="G162" s="10" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="H162" s="9" t="inlineStr"/>
@@ -7686,17 +7622,17 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>Super + Print Screen</t>
+          <t>Super + Shift + Y</t>
         </is>
       </c>
       <c r="C163" s="9" t="inlineStr">
         <is>
-          <t>Color picker</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E163" s="7" t="inlineStr">
@@ -7711,14 +7647,10 @@
       </c>
       <c r="G163" s="10" t="inlineStr">
         <is>
-          <t>rebind</t>
-        </is>
-      </c>
-      <c r="H163" s="9" t="inlineStr">
-        <is>
-          <t>Sounds usefull, but I don't have a print screen button.</t>
-        </is>
-      </c>
+          <t>Remove</t>
+        </is>
+      </c>
+      <c r="H163" s="9" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="7" t="n">
@@ -7726,17 +7658,17 @@
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + Print Screen</t>
+          <t>Super + Shift + Alt + G</t>
         </is>
       </c>
       <c r="C164" s="9" t="inlineStr">
         <is>
-          <t>Extract text (OCR) from screenshot</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D164" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E164" s="7" t="inlineStr">
@@ -7762,17 +7694,17 @@
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + S</t>
+          <t>Super + Shift + Ctrl + G</t>
         </is>
       </c>
       <c r="C165" s="9" t="inlineStr">
         <is>
-          <t>Share</t>
+          <t>Google Messages</t>
         </is>
       </c>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E165" s="7" t="inlineStr">
@@ -7787,7 +7719,7 @@
       </c>
       <c r="G165" s="10" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="H165" s="9" t="inlineStr"/>
@@ -7798,17 +7730,17 @@
       </c>
       <c r="B166" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + .</t>
+          <t>Super + Shift + P</t>
         </is>
       </c>
       <c r="C166" s="9" t="inlineStr">
         <is>
-          <t>Transcode</t>
+          <t>Google Photos</t>
         </is>
       </c>
       <c r="D166" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E166" s="7" t="inlineStr">
@@ -7823,7 +7755,7 @@
       </c>
       <c r="G166" s="10" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="H166" s="9" t="inlineStr"/>
@@ -7834,17 +7766,17 @@
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + R</t>
+          <t>Super + Shift + S</t>
         </is>
       </c>
       <c r="C167" s="9" t="inlineStr">
         <is>
-          <t>Set reminder</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>Menus, capture &amp; system</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="E167" s="7" t="inlineStr">
@@ -7857,11 +7789,7 @@
           <t>Removed by you</t>
         </is>
       </c>
-      <c r="G167" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+      <c r="G167" s="10" t="n"/>
       <c r="H167" s="9" t="inlineStr"/>
     </row>
     <row r="168">
@@ -7870,12 +7798,12 @@
       </c>
       <c r="B168" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + Alt + R</t>
+          <t>Super + Alt + Space</t>
         </is>
       </c>
       <c r="C168" s="9" t="inlineStr">
         <is>
-          <t>Show reminders</t>
+          <t>Apps menu</t>
         </is>
       </c>
       <c r="D168" s="7" t="inlineStr">
@@ -7898,7 +7826,11 @@
           <t>remove</t>
         </is>
       </c>
-      <c r="H168" s="9" t="inlineStr"/>
+      <c r="H168" s="9" t="inlineStr">
+        <is>
+          <t>I use super+space for looking for apps</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="7" t="n">
@@ -7906,12 +7838,12 @@
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Ctrl + R</t>
+          <t>Super + Ctrl + C</t>
         </is>
       </c>
       <c r="C169" s="9" t="inlineStr">
         <is>
-          <t>Clear reminders</t>
+          <t>Capture menu</t>
         </is>
       </c>
       <c r="D169" s="7" t="inlineStr">
@@ -7931,7 +7863,7 @@
       </c>
       <c r="G169" s="10" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="H169" s="9" t="inlineStr"/>
@@ -7942,12 +7874,12 @@
       </c>
       <c r="B170" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + Alt + T</t>
+          <t>Super + Ctrl + H</t>
         </is>
       </c>
       <c r="C170" s="9" t="inlineStr">
         <is>
-          <t>Show time</t>
+          <t>Hardware menu</t>
         </is>
       </c>
       <c r="D170" s="7" t="inlineStr">
@@ -7967,10 +7899,14 @@
       </c>
       <c r="G170" s="10" t="inlineStr">
         <is>
-          <t>remove</t>
-        </is>
-      </c>
-      <c r="H170" s="9" t="inlineStr"/>
+          <t>Remove</t>
+        </is>
+      </c>
+      <c r="H170" s="9" t="inlineStr">
+        <is>
+          <t>Doesn't seem  to do anything for me.</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="7" t="n">
@@ -7978,12 +7914,12 @@
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + Alt + B</t>
+          <t>Super + Shift + code:201</t>
         </is>
       </c>
       <c r="C171" s="9" t="inlineStr">
         <is>
-          <t>Show battery remaining</t>
+          <t>Omarchy menu</t>
         </is>
       </c>
       <c r="D171" s="7" t="inlineStr">
@@ -8003,7 +7939,7 @@
       </c>
       <c r="G171" s="10" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="H171" s="9" t="inlineStr"/>
@@ -8014,12 +7950,12 @@
       </c>
       <c r="B172" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + Alt + W</t>
+          <t>Super + Alt + K</t>
         </is>
       </c>
       <c r="C172" s="9" t="inlineStr">
         <is>
-          <t>Toggle weather</t>
+          <t>Tmux keybindings</t>
         </is>
       </c>
       <c r="D172" s="7" t="inlineStr">
@@ -8039,7 +7975,7 @@
       </c>
       <c r="G172" s="10" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="H172" s="9" t="inlineStr"/>
@@ -8050,12 +7986,12 @@
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + Ctrl + A</t>
+          <t>Super + Ctrl + Q</t>
         </is>
       </c>
       <c r="C173" s="9" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>Calculator</t>
         </is>
       </c>
       <c r="D173" s="7" t="inlineStr">
@@ -8070,10 +8006,14 @@
       </c>
       <c r="F173" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G173" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G173" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H173" s="9" t="inlineStr"/>
     </row>
     <row r="174">
@@ -8082,12 +8022,12 @@
       </c>
       <c r="B174" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + A</t>
+          <t>Super + Shift + Space</t>
         </is>
       </c>
       <c r="C174" s="9" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>Toggle top bar</t>
         </is>
       </c>
       <c r="D174" s="7" t="inlineStr">
@@ -8107,7 +8047,7 @@
       </c>
       <c r="G174" s="10" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>remove</t>
         </is>
       </c>
       <c r="H174" s="9" t="inlineStr"/>
@@ -8118,12 +8058,12 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + B</t>
+          <t>Super + Backspace</t>
         </is>
       </c>
       <c r="C175" s="9" t="inlineStr">
         <is>
-          <t>Bluetooth</t>
+          <t>Toggle window transparency</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
@@ -8146,7 +8086,11 @@
           <t>remove</t>
         </is>
       </c>
-      <c r="H175" s="9" t="inlineStr"/>
+      <c r="H175" s="9" t="inlineStr">
+        <is>
+          <t>Make sure we have transparentcy turned off first.</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="7" t="n">
@@ -8154,12 +8098,12 @@
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + D</t>
+          <t>Super + Shift + Backspace</t>
         </is>
       </c>
       <c r="C176" s="9" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Toggle window gaps</t>
         </is>
       </c>
       <c r="D176" s="7" t="inlineStr">
@@ -8177,11 +8121,7 @@
           <t>Removed by you</t>
         </is>
       </c>
-      <c r="G176" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
+      <c r="G176" s="10" t="n"/>
       <c r="H176" s="9" t="inlineStr"/>
     </row>
     <row r="177">
@@ -8190,12 +8130,12 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + Alt + D</t>
+          <t>Super + Ctrl + Backspace</t>
         </is>
       </c>
       <c r="C177" s="9" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Toggle single-window square aspect</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
@@ -8226,12 +8166,12 @@
       </c>
       <c r="B178" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + W</t>
+          <t>Super + ,</t>
         </is>
       </c>
       <c r="C178" s="9" t="inlineStr">
         <is>
-          <t>Network</t>
+          <t>Dismiss last notification</t>
         </is>
       </c>
       <c r="D178" s="7" t="inlineStr">
@@ -8246,15 +8186,19 @@
       </c>
       <c r="F178" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
+          <t>Replaced by yours</t>
         </is>
       </c>
       <c r="G178" s="10" t="inlineStr">
         <is>
-          <t>remove</t>
-        </is>
-      </c>
-      <c r="H178" s="9" t="inlineStr"/>
+          <t>rebind</t>
+        </is>
+      </c>
+      <c r="H178" s="9" t="inlineStr">
+        <is>
+          <t>Now: Dismiss all notifications</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="7" t="n">
@@ -8262,12 +8206,12 @@
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + P</t>
+          <t>Super + Shift + ,</t>
         </is>
       </c>
       <c r="C179" s="9" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Dismiss all notifications</t>
         </is>
       </c>
       <c r="D179" s="7" t="inlineStr">
@@ -8298,12 +8242,12 @@
       </c>
       <c r="B180" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + T</t>
+          <t>Super + Ctrl + ,</t>
         </is>
       </c>
       <c r="C180" s="9" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Toggle silencing notifications</t>
         </is>
       </c>
       <c r="D180" s="7" t="inlineStr">
@@ -8318,10 +8262,14 @@
       </c>
       <c r="F180" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G180" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G180" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H180" s="9" t="inlineStr"/>
     </row>
     <row r="181">
@@ -8330,12 +8278,12 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + 1</t>
+          <t>Super + Shift + Alt + ,</t>
         </is>
       </c>
       <c r="C181" s="9" t="inlineStr">
         <is>
-          <t>Bar panel 1</t>
+          <t>Open notification history</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
@@ -8366,12 +8314,12 @@
       </c>
       <c r="B182" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + 2</t>
+          <t>Super + Ctrl + I</t>
         </is>
       </c>
       <c r="C182" s="9" t="inlineStr">
         <is>
-          <t>Bar panel 2</t>
+          <t>Toggle locking on idle</t>
         </is>
       </c>
       <c r="D182" s="7" t="inlineStr">
@@ -8402,12 +8350,12 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + 3</t>
+          <t>Super + Ctrl + N</t>
         </is>
       </c>
       <c r="C183" s="9" t="inlineStr">
         <is>
-          <t>Bar panel 3</t>
+          <t>Toggle nightlight</t>
         </is>
       </c>
       <c r="D183" s="7" t="inlineStr">
@@ -8438,12 +8386,12 @@
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + 4</t>
+          <t>Super + Ctrl + Delete</t>
         </is>
       </c>
       <c r="C184" s="9" t="inlineStr">
         <is>
-          <t>Bar panel 4</t>
+          <t>Toggle laptop display</t>
         </is>
       </c>
       <c r="D184" s="7" t="inlineStr">
@@ -8458,7 +8406,7 @@
       </c>
       <c r="F184" s="7" t="inlineStr">
         <is>
-          <t>Replaced by yours</t>
+          <t>Removed by you</t>
         </is>
       </c>
       <c r="G184" s="10" t="inlineStr">
@@ -8466,11 +8414,7 @@
           <t>remove</t>
         </is>
       </c>
-      <c r="H184" s="9" t="inlineStr">
-        <is>
-          <t>Now: Screenshot</t>
-        </is>
-      </c>
+      <c r="H184" s="9" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="7" t="n">
@@ -8478,12 +8422,12 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + 5</t>
+          <t>Super + Ctrl + Alt + Delete</t>
         </is>
       </c>
       <c r="C185" s="9" t="inlineStr">
         <is>
-          <t>Bar panel 5</t>
+          <t>Toggle laptop display mirroring</t>
         </is>
       </c>
       <c r="D185" s="7" t="inlineStr">
@@ -8498,7 +8442,7 @@
       </c>
       <c r="F185" s="7" t="inlineStr">
         <is>
-          <t>Replaced by yours</t>
+          <t>Removed by you</t>
         </is>
       </c>
       <c r="G185" s="10" t="inlineStr">
@@ -8506,11 +8450,7 @@
           <t>remove</t>
         </is>
       </c>
-      <c r="H185" s="9" t="inlineStr">
-        <is>
-          <t>Now: Screenrecording</t>
-        </is>
-      </c>
+      <c r="H185" s="9" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="7" t="n">
@@ -8518,12 +8458,12 @@
       </c>
       <c r="B186" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + 6</t>
+          <t>Print Screen</t>
         </is>
       </c>
       <c r="C186" s="9" t="inlineStr">
         <is>
-          <t>Bar panel 6</t>
+          <t>Screenshot</t>
         </is>
       </c>
       <c r="D186" s="7" t="inlineStr">
@@ -8538,7 +8478,7 @@
       </c>
       <c r="F186" s="7" t="inlineStr">
         <is>
-          <t>Replaced by yours</t>
+          <t>Removed by you</t>
         </is>
       </c>
       <c r="G186" s="10" t="inlineStr">
@@ -8546,11 +8486,7 @@
           <t>remove</t>
         </is>
       </c>
-      <c r="H186" s="9" t="inlineStr">
-        <is>
-          <t>Now: Color picker</t>
-        </is>
-      </c>
+      <c r="H186" s="9" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="7" t="n">
@@ -8558,12 +8494,12 @@
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + 7</t>
+          <t>Alt + Print Screen</t>
         </is>
       </c>
       <c r="C187" s="9" t="inlineStr">
         <is>
-          <t>Bar panel 7</t>
+          <t>Screenrecording</t>
         </is>
       </c>
       <c r="D187" s="7" t="inlineStr">
@@ -8583,10 +8519,14 @@
       </c>
       <c r="G187" s="10" t="inlineStr">
         <is>
-          <t>remove</t>
-        </is>
-      </c>
-      <c r="H187" s="9" t="inlineStr"/>
+          <t>rebind</t>
+        </is>
+      </c>
+      <c r="H187" s="9" t="inlineStr">
+        <is>
+          <t>super+ctrl+5</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="7" t="n">
@@ -8594,12 +8534,12 @@
       </c>
       <c r="B188" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + 8</t>
+          <t>Super + Alt + code:34</t>
         </is>
       </c>
       <c r="C188" s="9" t="inlineStr">
         <is>
-          <t>Bar panel 8</t>
+          <t>Make webcam overlay smaller</t>
         </is>
       </c>
       <c r="D188" s="7" t="inlineStr">
@@ -8630,12 +8570,12 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + 9</t>
+          <t>Super + Alt + code:35</t>
         </is>
       </c>
       <c r="C189" s="9" t="inlineStr">
         <is>
-          <t>Bar panel 9</t>
+          <t>Make webcam overlay larger</t>
         </is>
       </c>
       <c r="D189" s="7" t="inlineStr">
@@ -8666,12 +8606,12 @@
       </c>
       <c r="B190" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + Z</t>
+          <t>Super + Print Screen</t>
         </is>
       </c>
       <c r="C190" s="9" t="inlineStr">
         <is>
-          <t>Zoom in</t>
+          <t>Color picker</t>
         </is>
       </c>
       <c r="D190" s="7" t="inlineStr">
@@ -8691,10 +8631,14 @@
       </c>
       <c r="G190" s="10" t="inlineStr">
         <is>
-          <t>remove</t>
-        </is>
-      </c>
-      <c r="H190" s="9" t="inlineStr"/>
+          <t>rebind</t>
+        </is>
+      </c>
+      <c r="H190" s="9" t="inlineStr">
+        <is>
+          <t>Sounds usefull, but I don't have a print screen button.</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="7" t="n">
@@ -8702,12 +8646,12 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + Alt + Z</t>
+          <t>Super + Ctrl + Print Screen</t>
         </is>
       </c>
       <c r="C191" s="9" t="inlineStr">
         <is>
-          <t>Reset zoom</t>
+          <t>Extract text (OCR) from screenshot</t>
         </is>
       </c>
       <c r="D191" s="7" t="inlineStr">
@@ -8727,7 +8671,7 @@
       </c>
       <c r="G191" s="10" t="inlineStr">
         <is>
-          <t>remove</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="H191" s="9" t="inlineStr"/>
@@ -8738,12 +8682,12 @@
       </c>
       <c r="B192" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + L</t>
+          <t>Super + Ctrl + S</t>
         </is>
       </c>
       <c r="C192" s="9" t="inlineStr">
         <is>
-          <t>Lock system</t>
+          <t>Share</t>
         </is>
       </c>
       <c r="D192" s="7" t="inlineStr">
@@ -8758,10 +8702,14 @@
       </c>
       <c r="F192" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G192" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G192" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H192" s="9" t="inlineStr"/>
     </row>
     <row r="193">
@@ -8770,17 +8718,17 @@
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>AudioRaiseVolume key</t>
+          <t>Super + Ctrl + .</t>
         </is>
       </c>
       <c r="C193" s="9" t="inlineStr">
         <is>
-          <t>Volume up</t>
+          <t>Transcode</t>
         </is>
       </c>
       <c r="D193" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E193" s="7" t="inlineStr">
@@ -8790,10 +8738,14 @@
       </c>
       <c r="F193" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G193" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G193" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H193" s="9" t="inlineStr"/>
     </row>
     <row r="194">
@@ -8802,17 +8754,17 @@
       </c>
       <c r="B194" s="8" t="inlineStr">
         <is>
-          <t>AudioLowerVolume key</t>
+          <t>Super + Ctrl + R</t>
         </is>
       </c>
       <c r="C194" s="9" t="inlineStr">
         <is>
-          <t>Volume down</t>
+          <t>Set reminder</t>
         </is>
       </c>
       <c r="D194" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E194" s="7" t="inlineStr">
@@ -8822,10 +8774,14 @@
       </c>
       <c r="F194" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G194" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G194" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H194" s="9" t="inlineStr"/>
     </row>
     <row r="195">
@@ -8834,17 +8790,17 @@
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>AudioMute key</t>
+          <t>Super + Ctrl + Alt + R</t>
         </is>
       </c>
       <c r="C195" s="9" t="inlineStr">
         <is>
-          <t>Mute</t>
+          <t>Show reminders</t>
         </is>
       </c>
       <c r="D195" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E195" s="7" t="inlineStr">
@@ -8854,10 +8810,14 @@
       </c>
       <c r="F195" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G195" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G195" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H195" s="9" t="inlineStr"/>
     </row>
     <row r="196">
@@ -8866,17 +8826,17 @@
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>AudioMicMute key</t>
+          <t>Super + Shift + Ctrl + R</t>
         </is>
       </c>
       <c r="C196" s="9" t="inlineStr">
         <is>
-          <t>Mute microphone</t>
+          <t>Clear reminders</t>
         </is>
       </c>
       <c r="D196" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E196" s="7" t="inlineStr">
@@ -8886,10 +8846,14 @@
       </c>
       <c r="F196" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G196" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G196" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H196" s="9" t="inlineStr"/>
     </row>
     <row r="197">
@@ -8898,17 +8862,17 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>MonBrightnessUp key</t>
+          <t>Super + Ctrl + Alt + T</t>
         </is>
       </c>
       <c r="C197" s="9" t="inlineStr">
         <is>
-          <t>Brightness up</t>
+          <t>Show time</t>
         </is>
       </c>
       <c r="D197" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E197" s="7" t="inlineStr">
@@ -8918,15 +8882,15 @@
       </c>
       <c r="F197" s="7" t="inlineStr">
         <is>
-          <t>Replaced by yours</t>
-        </is>
-      </c>
-      <c r="G197" s="10" t="n"/>
-      <c r="H197" s="9" t="inlineStr">
-        <is>
-          <t>Now: Brightness up</t>
-        </is>
-      </c>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G197" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
+      <c r="H197" s="9" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="7" t="n">
@@ -8934,17 +8898,17 @@
       </c>
       <c r="B198" s="8" t="inlineStr">
         <is>
-          <t>MonBrightnessDown key</t>
+          <t>Super + Ctrl + Alt + B</t>
         </is>
       </c>
       <c r="C198" s="9" t="inlineStr">
         <is>
-          <t>Brightness down</t>
+          <t>Show battery remaining</t>
         </is>
       </c>
       <c r="D198" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E198" s="7" t="inlineStr">
@@ -8954,15 +8918,15 @@
       </c>
       <c r="F198" s="7" t="inlineStr">
         <is>
-          <t>Replaced by yours</t>
-        </is>
-      </c>
-      <c r="G198" s="10" t="n"/>
-      <c r="H198" s="9" t="inlineStr">
-        <is>
-          <t>Now: Brightness down</t>
-        </is>
-      </c>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G198" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
+      <c r="H198" s="9" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="7" t="n">
@@ -8970,17 +8934,17 @@
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>Shift + MonBrightnessUp key</t>
+          <t>Super + Ctrl + Alt + W</t>
         </is>
       </c>
       <c r="C199" s="9" t="inlineStr">
         <is>
-          <t>Brightness maximum</t>
+          <t>Toggle weather</t>
         </is>
       </c>
       <c r="D199" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E199" s="7" t="inlineStr">
@@ -8990,15 +8954,15 @@
       </c>
       <c r="F199" s="7" t="inlineStr">
         <is>
-          <t>Replaced by yours</t>
-        </is>
-      </c>
-      <c r="G199" s="10" t="n"/>
-      <c r="H199" s="9" t="inlineStr">
-        <is>
-          <t>Now: Brightness maximum</t>
-        </is>
-      </c>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G199" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
+      <c r="H199" s="9" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="7" t="n">
@@ -9006,17 +8970,17 @@
       </c>
       <c r="B200" s="8" t="inlineStr">
         <is>
-          <t>Shift + MonBrightnessDown key</t>
+          <t>Super + Ctrl + A</t>
         </is>
       </c>
       <c r="C200" s="9" t="inlineStr">
         <is>
-          <t>Brightness minimum</t>
+          <t>Audio</t>
         </is>
       </c>
       <c r="D200" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E200" s="7" t="inlineStr">
@@ -9026,15 +8990,15 @@
       </c>
       <c r="F200" s="7" t="inlineStr">
         <is>
-          <t>Replaced by yours</t>
-        </is>
-      </c>
-      <c r="G200" s="10" t="n"/>
-      <c r="H200" s="9" t="inlineStr">
-        <is>
-          <t>Now: Brightness minimum</t>
-        </is>
-      </c>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G200" s="10" t="inlineStr">
+        <is>
+          <t>Remove</t>
+        </is>
+      </c>
+      <c r="H200" s="9" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="7" t="n">
@@ -9042,17 +9006,17 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>KbdBrightnessUp key</t>
+          <t>Super + Ctrl + B</t>
         </is>
       </c>
       <c r="C201" s="9" t="inlineStr">
         <is>
-          <t>Keyboard brightness up</t>
+          <t>Bluetooth</t>
         </is>
       </c>
       <c r="D201" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E201" s="7" t="inlineStr">
@@ -9078,17 +9042,17 @@
       </c>
       <c r="B202" s="8" t="inlineStr">
         <is>
-          <t>KbdBrightnessDown key</t>
+          <t>Super + Ctrl + D</t>
         </is>
       </c>
       <c r="C202" s="9" t="inlineStr">
         <is>
-          <t>Keyboard brightness down</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="D202" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E202" s="7" t="inlineStr">
@@ -9114,17 +9078,17 @@
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>KbdLightOnOff key</t>
+          <t>Super + Ctrl + Alt + D</t>
         </is>
       </c>
       <c r="C203" s="9" t="inlineStr">
         <is>
-          <t>Keyboard backlight cycle</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="D203" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E203" s="7" t="inlineStr">
@@ -9150,17 +9114,17 @@
       </c>
       <c r="B204" s="8" t="inlineStr">
         <is>
-          <t>TouchpadToggle key</t>
+          <t>Super + Ctrl + W</t>
         </is>
       </c>
       <c r="C204" s="9" t="inlineStr">
         <is>
-          <t>Toggle touchpad</t>
+          <t>Network</t>
         </is>
       </c>
       <c r="D204" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E204" s="7" t="inlineStr">
@@ -9186,17 +9150,17 @@
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>TouchpadOn key</t>
+          <t>Super + Ctrl + P</t>
         </is>
       </c>
       <c r="C205" s="9" t="inlineStr">
         <is>
-          <t>Enable touchpad</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="D205" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E205" s="7" t="inlineStr">
@@ -9222,17 +9186,17 @@
       </c>
       <c r="B206" s="8" t="inlineStr">
         <is>
-          <t>TouchpadOff key</t>
+          <t>Super + Ctrl + 1</t>
         </is>
       </c>
       <c r="C206" s="9" t="inlineStr">
         <is>
-          <t>Disable touchpad</t>
+          <t>Bar panel 1</t>
         </is>
       </c>
       <c r="D206" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E206" s="7" t="inlineStr">
@@ -9258,17 +9222,17 @@
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>Alt + AudioRaiseVolume key</t>
+          <t>Super + Ctrl + 2</t>
         </is>
       </c>
       <c r="C207" s="9" t="inlineStr">
         <is>
-          <t>Volume up precise</t>
+          <t>Bar panel 2</t>
         </is>
       </c>
       <c r="D207" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E207" s="7" t="inlineStr">
@@ -9278,10 +9242,14 @@
       </c>
       <c r="F207" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G207" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G207" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H207" s="9" t="inlineStr"/>
     </row>
     <row r="208">
@@ -9290,17 +9258,17 @@
       </c>
       <c r="B208" s="8" t="inlineStr">
         <is>
-          <t>Alt + AudioLowerVolume key</t>
+          <t>Super + Ctrl + 3</t>
         </is>
       </c>
       <c r="C208" s="9" t="inlineStr">
         <is>
-          <t>Volume down precise</t>
+          <t>Bar panel 3</t>
         </is>
       </c>
       <c r="D208" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E208" s="7" t="inlineStr">
@@ -9310,10 +9278,14 @@
       </c>
       <c r="F208" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G208" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G208" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H208" s="9" t="inlineStr"/>
     </row>
     <row r="209">
@@ -9322,17 +9294,17 @@
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
-          <t>Alt + MonBrightnessUp key</t>
+          <t>Super + Ctrl + 4</t>
         </is>
       </c>
       <c r="C209" s="9" t="inlineStr">
         <is>
-          <t>Brightness up precise</t>
+          <t>Bar panel 4</t>
         </is>
       </c>
       <c r="D209" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E209" s="7" t="inlineStr">
@@ -9345,10 +9317,14 @@
           <t>Replaced by yours</t>
         </is>
       </c>
-      <c r="G209" s="10" t="n"/>
+      <c r="G209" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H209" s="9" t="inlineStr">
         <is>
-          <t>Now: Brightness up precise</t>
+          <t>Now: Screenshot</t>
         </is>
       </c>
     </row>
@@ -9358,17 +9334,17 @@
       </c>
       <c r="B210" s="8" t="inlineStr">
         <is>
-          <t>Alt + MonBrightnessDown key</t>
+          <t>Super + Ctrl + 5</t>
         </is>
       </c>
       <c r="C210" s="9" t="inlineStr">
         <is>
-          <t>Brightness down precise</t>
+          <t>Bar panel 5</t>
         </is>
       </c>
       <c r="D210" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E210" s="7" t="inlineStr">
@@ -9381,10 +9357,14 @@
           <t>Replaced by yours</t>
         </is>
       </c>
-      <c r="G210" s="10" t="n"/>
+      <c r="G210" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H210" s="9" t="inlineStr">
         <is>
-          <t>Now: Brightness down precise</t>
+          <t>Now: Screenrecording</t>
         </is>
       </c>
     </row>
@@ -9394,17 +9374,17 @@
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>AudioNext key</t>
+          <t>Super + Ctrl + 6</t>
         </is>
       </c>
       <c r="C211" s="9" t="inlineStr">
         <is>
-          <t>Next track</t>
+          <t>Bar panel 6</t>
         </is>
       </c>
       <c r="D211" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E211" s="7" t="inlineStr">
@@ -9414,7 +9394,7 @@
       </c>
       <c r="F211" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
+          <t>Replaced by yours</t>
         </is>
       </c>
       <c r="G211" s="10" t="inlineStr">
@@ -9422,7 +9402,11 @@
           <t>remove</t>
         </is>
       </c>
-      <c r="H211" s="9" t="inlineStr"/>
+      <c r="H211" s="9" t="inlineStr">
+        <is>
+          <t>Now: Color picker</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="7" t="n">
@@ -9430,17 +9414,17 @@
       </c>
       <c r="B212" s="8" t="inlineStr">
         <is>
-          <t>Alt + AudioPlay key</t>
+          <t>Super + Ctrl + 7</t>
         </is>
       </c>
       <c r="C212" s="9" t="inlineStr">
         <is>
-          <t>Next track</t>
+          <t>Bar panel 7</t>
         </is>
       </c>
       <c r="D212" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E212" s="7" t="inlineStr">
@@ -9466,17 +9450,17 @@
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>AudioPause key</t>
+          <t>Super + Ctrl + 8</t>
         </is>
       </c>
       <c r="C213" s="9" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Bar panel 8</t>
         </is>
       </c>
       <c r="D213" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E213" s="7" t="inlineStr">
@@ -9502,17 +9486,17 @@
       </c>
       <c r="B214" s="8" t="inlineStr">
         <is>
-          <t>AudioPlay key</t>
+          <t>Super + Ctrl + 9</t>
         </is>
       </c>
       <c r="C214" s="9" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Bar panel 9</t>
         </is>
       </c>
       <c r="D214" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E214" s="7" t="inlineStr">
@@ -9538,17 +9522,17 @@
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>AudioPrev key</t>
+          <t>Super + Ctrl + Z</t>
         </is>
       </c>
       <c r="C215" s="9" t="inlineStr">
         <is>
-          <t>Previous track</t>
+          <t>Zoom in</t>
         </is>
       </c>
       <c r="D215" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E215" s="7" t="inlineStr">
@@ -9574,17 +9558,17 @@
       </c>
       <c r="B216" s="8" t="inlineStr">
         <is>
-          <t>Alt + Shift + AudioPlay key</t>
+          <t>Super + Ctrl + Alt + Z</t>
         </is>
       </c>
       <c r="C216" s="9" t="inlineStr">
         <is>
-          <t>Previous track</t>
+          <t>Reset zoom</t>
         </is>
       </c>
       <c r="D216" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E216" s="7" t="inlineStr">
@@ -9610,17 +9594,17 @@
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>Eject key</t>
+          <t>Super + Ctrl + V</t>
         </is>
       </c>
       <c r="C217" s="9" t="inlineStr">
         <is>
-          <t>Eject media</t>
+          <t>Clipboard manager</t>
         </is>
       </c>
       <c r="D217" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Clipboard</t>
         </is>
       </c>
       <c r="E217" s="7" t="inlineStr">
@@ -9646,17 +9630,17 @@
       </c>
       <c r="B218" s="8" t="inlineStr">
         <is>
-          <t>Shift + AudioMute key</t>
+          <t>F9</t>
         </is>
       </c>
       <c r="C218" s="9" t="inlineStr">
         <is>
-          <t>Switch audio output</t>
+          <t>Start dictation (push-to-talk); Stop dictation (push-to-talk)</t>
         </is>
       </c>
       <c r="D218" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Dictation</t>
         </is>
       </c>
       <c r="E218" s="7" t="inlineStr">
@@ -9682,17 +9666,17 @@
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>Shift + AudioPause key</t>
+          <t>Calculator key</t>
         </is>
       </c>
       <c r="C219" s="9" t="inlineStr">
         <is>
-          <t>Switch media source</t>
+          <t>Calculator</t>
         </is>
       </c>
       <c r="D219" s="7" t="inlineStr">
         <is>
-          <t>Volume, media &amp; brightness</t>
+          <t>Menus, capture &amp; system</t>
         </is>
       </c>
       <c r="E219" s="7" t="inlineStr">
@@ -9718,12 +9702,12 @@
       </c>
       <c r="B220" s="8" t="inlineStr">
         <is>
-          <t>Shift + AudioPlay key</t>
+          <t>MonBrightnessUp key</t>
         </is>
       </c>
       <c r="C220" s="9" t="inlineStr">
         <is>
-          <t>Switch media source</t>
+          <t>Brightness up</t>
         </is>
       </c>
       <c r="D220" s="7" t="inlineStr">
@@ -9738,15 +9722,15 @@
       </c>
       <c r="F220" s="7" t="inlineStr">
         <is>
-          <t>Removed by you</t>
-        </is>
-      </c>
-      <c r="G220" s="10" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
-      <c r="H220" s="9" t="inlineStr"/>
+          <t>Replaced by yours</t>
+        </is>
+      </c>
+      <c r="G220" s="10" t="n"/>
+      <c r="H220" s="9" t="inlineStr">
+        <is>
+          <t>Now: Brightness up</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="7" t="n">
@@ -9754,17 +9738,17 @@
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>Super + C</t>
+          <t>MonBrightnessDown key</t>
         </is>
       </c>
       <c r="C221" s="9" t="inlineStr">
         <is>
-          <t>Universal copy</t>
+          <t>Brightness down</t>
         </is>
       </c>
       <c r="D221" s="7" t="inlineStr">
         <is>
-          <t>Clipboard</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E221" s="7" t="inlineStr">
@@ -9774,11 +9758,15 @@
       </c>
       <c r="F221" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Replaced by yours</t>
         </is>
       </c>
       <c r="G221" s="10" t="n"/>
-      <c r="H221" s="9" t="inlineStr"/>
+      <c r="H221" s="9" t="inlineStr">
+        <is>
+          <t>Now: Brightness down</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="7" t="n">
@@ -9786,17 +9774,17 @@
       </c>
       <c r="B222" s="8" t="inlineStr">
         <is>
-          <t>Super + V</t>
+          <t>Shift + MonBrightnessUp key</t>
         </is>
       </c>
       <c r="C222" s="9" t="inlineStr">
         <is>
-          <t>Universal paste</t>
+          <t>Brightness maximum</t>
         </is>
       </c>
       <c r="D222" s="7" t="inlineStr">
         <is>
-          <t>Clipboard</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E222" s="7" t="inlineStr">
@@ -9806,11 +9794,15 @@
       </c>
       <c r="F222" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Replaced by yours</t>
         </is>
       </c>
       <c r="G222" s="10" t="n"/>
-      <c r="H222" s="9" t="inlineStr"/>
+      <c r="H222" s="9" t="inlineStr">
+        <is>
+          <t>Now: Brightness maximum</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="7" t="n">
@@ -9818,17 +9810,17 @@
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>Super + X</t>
+          <t>Shift + MonBrightnessDown key</t>
         </is>
       </c>
       <c r="C223" s="9" t="inlineStr">
         <is>
-          <t>Universal cut</t>
+          <t>Brightness minimum</t>
         </is>
       </c>
       <c r="D223" s="7" t="inlineStr">
         <is>
-          <t>Clipboard</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E223" s="7" t="inlineStr">
@@ -9838,11 +9830,15 @@
       </c>
       <c r="F223" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Replaced by yours</t>
         </is>
       </c>
       <c r="G223" s="10" t="n"/>
-      <c r="H223" s="9" t="inlineStr"/>
+      <c r="H223" s="9" t="inlineStr">
+        <is>
+          <t>Now: Brightness minimum</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="7" t="n">
@@ -9850,17 +9846,17 @@
       </c>
       <c r="B224" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + V</t>
+          <t>KbdBrightnessUp key</t>
         </is>
       </c>
       <c r="C224" s="9" t="inlineStr">
         <is>
-          <t>Clipboard manager</t>
+          <t>Keyboard brightness up</t>
         </is>
       </c>
       <c r="D224" s="7" t="inlineStr">
         <is>
-          <t>Clipboard</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E224" s="7" t="inlineStr">
@@ -9886,17 +9882,17 @@
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + X</t>
+          <t>KbdBrightnessDown key</t>
         </is>
       </c>
       <c r="C225" s="9" t="inlineStr">
         <is>
-          <t>Toggle dictation</t>
+          <t>Keyboard brightness down</t>
         </is>
       </c>
       <c r="D225" s="7" t="inlineStr">
         <is>
-          <t>Dictation</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E225" s="7" t="inlineStr">
@@ -9906,10 +9902,14 @@
       </c>
       <c r="F225" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G225" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G225" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H225" s="9" t="inlineStr"/>
     </row>
     <row r="226">
@@ -9918,17 +9918,17 @@
       </c>
       <c r="B226" s="8" t="inlineStr">
         <is>
-          <t>F9</t>
+          <t>KbdLightOnOff key</t>
         </is>
       </c>
       <c r="C226" s="9" t="inlineStr">
         <is>
-          <t>Start dictation (push-to-talk); Stop dictation (push-to-talk)</t>
+          <t>Keyboard backlight cycle</t>
         </is>
       </c>
       <c r="D226" s="7" t="inlineStr">
         <is>
-          <t>Dictation</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E226" s="7" t="inlineStr">
@@ -9954,30 +9954,34 @@
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t>Super + Q</t>
+          <t>TouchpadToggle key</t>
         </is>
       </c>
       <c r="C227" s="9" t="inlineStr">
         <is>
-          <t>Close window</t>
+          <t>Toggle touchpad</t>
         </is>
       </c>
       <c r="D227" s="7" t="inlineStr">
         <is>
-          <t>Yours</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E227" s="7" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Omarchy</t>
         </is>
       </c>
       <c r="F227" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G227" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G227" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H227" s="9" t="inlineStr"/>
     </row>
     <row r="228">
@@ -9986,30 +9990,34 @@
       </c>
       <c r="B228" s="8" t="inlineStr">
         <is>
-          <t>Super + A</t>
+          <t>TouchpadOn key</t>
         </is>
       </c>
       <c r="C228" s="9" t="inlineStr">
         <is>
-          <t>Universal select all</t>
+          <t>Enable touchpad</t>
         </is>
       </c>
       <c r="D228" s="7" t="inlineStr">
         <is>
-          <t>Yours</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E228" s="7" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Omarchy</t>
         </is>
       </c>
       <c r="F228" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G228" s="10" t="n"/>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G228" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
       <c r="H228" s="9" t="inlineStr"/>
     </row>
     <row r="229">
@@ -10018,35 +10026,35 @@
       </c>
       <c r="B229" s="8" t="inlineStr">
         <is>
-          <t>Super + S</t>
+          <t>TouchpadOff key</t>
         </is>
       </c>
       <c r="C229" s="9" t="inlineStr">
         <is>
-          <t>Universal save</t>
+          <t>Disable touchpad</t>
         </is>
       </c>
       <c r="D229" s="7" t="inlineStr">
         <is>
-          <t>Yours</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E229" s="7" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Omarchy</t>
         </is>
       </c>
       <c r="F229" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G229" s="10" t="n"/>
-      <c r="H229" s="9" t="inlineStr">
-        <is>
-          <t>Replaces an Omarchy default</t>
-        </is>
-      </c>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G229" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
+      <c r="H229" s="9" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="7" t="n">
@@ -10054,33 +10062,33 @@
       </c>
       <c r="B230" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + F</t>
+          <t>Alt + MonBrightnessUp key</t>
         </is>
       </c>
       <c r="C230" s="9" t="inlineStr">
         <is>
-          <t>File manager (cwd)</t>
+          <t>Brightness up precise</t>
         </is>
       </c>
       <c r="D230" s="7" t="inlineStr">
         <is>
-          <t>Yours</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E230" s="7" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Omarchy</t>
         </is>
       </c>
       <c r="F230" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Replaced by yours</t>
         </is>
       </c>
       <c r="G230" s="10" t="n"/>
       <c r="H230" s="9" t="inlineStr">
         <is>
-          <t>Replaces an Omarchy default</t>
+          <t>Now: Brightness up precise</t>
         </is>
       </c>
     </row>
@@ -10090,33 +10098,33 @@
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>Super + ,</t>
+          <t>Alt + MonBrightnessDown key</t>
         </is>
       </c>
       <c r="C231" s="9" t="inlineStr">
         <is>
-          <t>Dismiss all notifications</t>
+          <t>Brightness down precise</t>
         </is>
       </c>
       <c r="D231" s="7" t="inlineStr">
         <is>
-          <t>Yours</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E231" s="7" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Omarchy</t>
         </is>
       </c>
       <c r="F231" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Replaced by yours</t>
         </is>
       </c>
       <c r="G231" s="10" t="n"/>
       <c r="H231" s="9" t="inlineStr">
         <is>
-          <t>Replaces an Omarchy default</t>
+          <t>Now: Brightness down precise</t>
         </is>
       </c>
     </row>
@@ -10126,35 +10134,35 @@
       </c>
       <c r="B232" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + 4</t>
+          <t>AudioNext key</t>
         </is>
       </c>
       <c r="C232" s="9" t="inlineStr">
         <is>
-          <t>Screenshot</t>
+          <t>Next track</t>
         </is>
       </c>
       <c r="D232" s="7" t="inlineStr">
         <is>
-          <t>Yours</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E232" s="7" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Omarchy</t>
         </is>
       </c>
       <c r="F232" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G232" s="10" t="n"/>
-      <c r="H232" s="9" t="inlineStr">
-        <is>
-          <t>Replaces an Omarchy default</t>
-        </is>
-      </c>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G232" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
+      <c r="H232" s="9" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="7" t="n">
@@ -10162,35 +10170,35 @@
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + 5</t>
+          <t>Alt + AudioPlay key</t>
         </is>
       </c>
       <c r="C233" s="9" t="inlineStr">
         <is>
-          <t>Screenrecording</t>
+          <t>Next track</t>
         </is>
       </c>
       <c r="D233" s="7" t="inlineStr">
         <is>
-          <t>Yours</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E233" s="7" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Omarchy</t>
         </is>
       </c>
       <c r="F233" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G233" s="10" t="n"/>
-      <c r="H233" s="9" t="inlineStr">
-        <is>
-          <t>Replaces an Omarchy default</t>
-        </is>
-      </c>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G233" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
+      <c r="H233" s="9" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="7" t="n">
@@ -10198,35 +10206,35 @@
       </c>
       <c r="B234" s="8" t="inlineStr">
         <is>
-          <t>Super + Ctrl + 6</t>
+          <t>AudioPause key</t>
         </is>
       </c>
       <c r="C234" s="9" t="inlineStr">
         <is>
-          <t>Color picker</t>
+          <t>Pause</t>
         </is>
       </c>
       <c r="D234" s="7" t="inlineStr">
         <is>
-          <t>Yours</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E234" s="7" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Omarchy</t>
         </is>
       </c>
       <c r="F234" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G234" s="10" t="n"/>
-      <c r="H234" s="9" t="inlineStr">
-        <is>
-          <t>Replaces an Omarchy default</t>
-        </is>
-      </c>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G234" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
+      <c r="H234" s="9" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="7" t="n">
@@ -10234,35 +10242,35 @@
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t>Super + Shift + M</t>
+          <t>AudioPlay key</t>
         </is>
       </c>
       <c r="C235" s="9" t="inlineStr">
         <is>
-          <t>Apple Music</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="D235" s="7" t="inlineStr">
         <is>
-          <t>Yours</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E235" s="7" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Omarchy</t>
         </is>
       </c>
       <c r="F235" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G235" s="10" t="n"/>
-      <c r="H235" s="9" t="inlineStr">
-        <is>
-          <t>Replaces an Omarchy default</t>
-        </is>
-      </c>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G235" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
+      <c r="H235" s="9" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="7" t="n">
@@ -10270,35 +10278,35 @@
       </c>
       <c r="B236" s="8" t="inlineStr">
         <is>
-          <t>MonBrightnessUp key</t>
+          <t>AudioPrev key</t>
         </is>
       </c>
       <c r="C236" s="9" t="inlineStr">
         <is>
-          <t>Brightness up</t>
+          <t>Previous track</t>
         </is>
       </c>
       <c r="D236" s="7" t="inlineStr">
         <is>
-          <t>Yours</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E236" s="7" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Omarchy</t>
         </is>
       </c>
       <c r="F236" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G236" s="10" t="n"/>
-      <c r="H236" s="9" t="inlineStr">
-        <is>
-          <t>Replaces an Omarchy default</t>
-        </is>
-      </c>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G236" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
+      <c r="H236" s="9" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="7" t="n">
@@ -10306,35 +10314,35 @@
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t>MonBrightnessDown key</t>
+          <t>Alt + Shift + AudioPlay key</t>
         </is>
       </c>
       <c r="C237" s="9" t="inlineStr">
         <is>
-          <t>Brightness down</t>
+          <t>Previous track</t>
         </is>
       </c>
       <c r="D237" s="7" t="inlineStr">
         <is>
-          <t>Yours</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E237" s="7" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Omarchy</t>
         </is>
       </c>
       <c r="F237" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G237" s="10" t="n"/>
-      <c r="H237" s="9" t="inlineStr">
-        <is>
-          <t>Replaces an Omarchy default</t>
-        </is>
-      </c>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G237" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
+      <c r="H237" s="9" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="7" t="n">
@@ -10342,35 +10350,35 @@
       </c>
       <c r="B238" s="8" t="inlineStr">
         <is>
-          <t>Shift + MonBrightnessUp key</t>
+          <t>Eject key</t>
         </is>
       </c>
       <c r="C238" s="9" t="inlineStr">
         <is>
-          <t>Brightness maximum</t>
+          <t>Eject media</t>
         </is>
       </c>
       <c r="D238" s="7" t="inlineStr">
         <is>
-          <t>Yours</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E238" s="7" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Omarchy</t>
         </is>
       </c>
       <c r="F238" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G238" s="10" t="n"/>
-      <c r="H238" s="9" t="inlineStr">
-        <is>
-          <t>Replaces an Omarchy default</t>
-        </is>
-      </c>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G238" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
+      <c r="H238" s="9" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="7" t="n">
@@ -10378,35 +10386,35 @@
       </c>
       <c r="B239" s="8" t="inlineStr">
         <is>
-          <t>Shift + MonBrightnessDown key</t>
+          <t>Shift + AudioMute key</t>
         </is>
       </c>
       <c r="C239" s="9" t="inlineStr">
         <is>
-          <t>Brightness minimum</t>
+          <t>Switch audio output</t>
         </is>
       </c>
       <c r="D239" s="7" t="inlineStr">
         <is>
-          <t>Yours</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E239" s="7" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Omarchy</t>
         </is>
       </c>
       <c r="F239" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G239" s="10" t="n"/>
-      <c r="H239" s="9" t="inlineStr">
-        <is>
-          <t>Replaces an Omarchy default</t>
-        </is>
-      </c>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G239" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
+      <c r="H239" s="9" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="7" t="n">
@@ -10414,35 +10422,35 @@
       </c>
       <c r="B240" s="8" t="inlineStr">
         <is>
-          <t>Alt + MonBrightnessUp key</t>
+          <t>Shift + AudioPause key</t>
         </is>
       </c>
       <c r="C240" s="9" t="inlineStr">
         <is>
-          <t>Brightness up precise</t>
+          <t>Switch media source</t>
         </is>
       </c>
       <c r="D240" s="7" t="inlineStr">
         <is>
-          <t>Yours</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E240" s="7" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Omarchy</t>
         </is>
       </c>
       <c r="F240" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G240" s="10" t="n"/>
-      <c r="H240" s="9" t="inlineStr">
-        <is>
-          <t>Replaces an Omarchy default</t>
-        </is>
-      </c>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G240" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
+      <c r="H240" s="9" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="7" t="n">
@@ -10450,35 +10458,35 @@
       </c>
       <c r="B241" s="8" t="inlineStr">
         <is>
-          <t>Alt + MonBrightnessDown key</t>
+          <t>Shift + AudioPlay key</t>
         </is>
       </c>
       <c r="C241" s="9" t="inlineStr">
         <is>
-          <t>Brightness down precise</t>
+          <t>Switch media source</t>
         </is>
       </c>
       <c r="D241" s="7" t="inlineStr">
         <is>
-          <t>Yours</t>
+          <t>Volume, media &amp; brightness</t>
         </is>
       </c>
       <c r="E241" s="7" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Omarchy</t>
         </is>
       </c>
       <c r="F241" s="7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G241" s="10" t="n"/>
-      <c r="H241" s="9" t="inlineStr">
-        <is>
-          <t>Replaces an Omarchy default</t>
-        </is>
-      </c>
+          <t>Removed by you</t>
+        </is>
+      </c>
+      <c r="G241" s="10" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
+      <c r="H241" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H241"/>
@@ -13807,7 +13815,7 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>[ B</t>
+          <t>[ b</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
@@ -13817,7 +13825,7 @@
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Move buffer prev</t>
+          <t>Prev Buffer</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
@@ -13839,7 +13847,7 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>[ b</t>
+          <t>[ B</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
@@ -13849,7 +13857,7 @@
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Prev Buffer</t>
+          <t>Move buffer prev</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
@@ -13935,7 +13943,7 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>] B</t>
+          <t>] b</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
@@ -13945,7 +13953,7 @@
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>Move buffer next</t>
+          <t>Next Buffer</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
@@ -13967,7 +13975,7 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>] b</t>
+          <t>] B</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
@@ -13977,7 +13985,7 @@
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Next Buffer</t>
+          <t>Move buffer next</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
@@ -14927,7 +14935,7 @@
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>Space c S</t>
+          <t>Space c s</t>
         </is>
       </c>
       <c r="C138" s="9" t="inlineStr">
@@ -14937,7 +14945,7 @@
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>LSP references/definitions/... (Trouble)</t>
+          <t>Symbols (Trouble)</t>
         </is>
       </c>
       <c r="E138" s="7" t="inlineStr">
@@ -14959,7 +14967,7 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>Space c s</t>
+          <t>Space c S</t>
         </is>
       </c>
       <c r="C139" s="9" t="inlineStr">
@@ -14969,7 +14977,7 @@
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>Symbols (Trouble)</t>
+          <t>LSP references/definitions/... (Trouble)</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr">
@@ -16303,7 +16311,7 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>Space q s</t>
+          <t>Space q S</t>
         </is>
       </c>
       <c r="C181" s="9" t="inlineStr">
@@ -16313,7 +16321,7 @@
       </c>
       <c r="D181" s="9" t="inlineStr">
         <is>
-          <t>Restore Session</t>
+          <t>Select Session</t>
         </is>
       </c>
       <c r="E181" s="7" t="inlineStr">
@@ -16335,7 +16343,7 @@
       </c>
       <c r="B182" s="8" t="inlineStr">
         <is>
-          <t>Space q S</t>
+          <t>Space q s</t>
         </is>
       </c>
       <c r="C182" s="9" t="inlineStr">
@@ -16345,7 +16353,7 @@
       </c>
       <c r="D182" s="9" t="inlineStr">
         <is>
-          <t>Select Session</t>
+          <t>Restore Session</t>
         </is>
       </c>
       <c r="E182" s="7" t="inlineStr">
@@ -17295,7 +17303,7 @@
       </c>
       <c r="B212" s="8" t="inlineStr">
         <is>
-          <t>Space s T</t>
+          <t>Space s t</t>
         </is>
       </c>
       <c r="C212" s="9" t="inlineStr">
@@ -17305,7 +17313,7 @@
       </c>
       <c r="D212" s="9" t="inlineStr">
         <is>
-          <t>Todo/Fix/Fixme</t>
+          <t>Todo</t>
         </is>
       </c>
       <c r="E212" s="7" t="inlineStr">
@@ -17327,7 +17335,7 @@
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>Space s t</t>
+          <t>Space s T</t>
         </is>
       </c>
       <c r="C213" s="9" t="inlineStr">
@@ -17337,7 +17345,7 @@
       </c>
       <c r="D213" s="9" t="inlineStr">
         <is>
-          <t>Todo</t>
+          <t>Todo/Fix/Fixme</t>
         </is>
       </c>
       <c r="E213" s="7" t="inlineStr">
